--- a/out/LSTM-Mamba1_repeat_2_000007.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7971993478774387</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.7971993478774387</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>4.242080543885407</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>4.242080543885407</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>4.242080543885407</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>4.242080543885407</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>4.242080543885407</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>4.242080543885407</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>4.242080543885407</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>4.242080543885407</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>4.242080543885407</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>3.642080543885407</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>3.642080543885407</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>3.642080543885407</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>3.642080543885407</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>4.242080543885407</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.1971993478774388</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.1971993478774388</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
-        <v>-8.49619523214642e-05</v>
+        <v>-6.75351114863297e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.9794857538496202</v>
+        <v>0.7785800168151985</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.960485767463571</v>
+        <v>1.558363729382479</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1468782580559186</v>
+        <v>0.1167515465921939</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.273441819022459</v>
+        <v>1.012241738182021</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1836456704050446</v>
+        <v>0.1459774784774187</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.493878181694815</v>
+        <v>1.18746364413097</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2632551976040997</v>
+        <v>0.209257860438623</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.836846545878087</v>
+        <v>1.460084593687064</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2816305678435452</v>
+        <v>0.2238644609173098</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
-        <v>2.136872808447906</v>
+        <v>1.698571628299907</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2984716366441283</v>
+        <v>0.237251944347076</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.452207605419116</v>
+        <v>1.949227299831098</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1346946984107789</v>
+        <v>0.1070667240257002</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.422877192868414</v>
+        <v>1.925912980847788</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.06505202606608947</v>
+        <v>0.05170897721724928</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.418179594771483</v>
+        <v>1.922178923545358</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03099535369839031</v>
+        <v>0.02463717527422079</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.41506661577477</v>
+        <v>1.919704459501471</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.00918151620237293</v>
+        <v>0.007297419349351257</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.402403469464549</v>
+        <v>1.909637419604475</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006071049223727566</v>
+        <v>0.004825271689484421</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.405361177390374</v>
+        <v>1.911987494252265</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003105282126212162</v>
+        <v>0.002466695254996821</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.405496116973147</v>
+        <v>1.912093724905556</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001585526177187189</v>
+        <v>0.001259367644650069</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.405561044259266</v>
+        <v>1.912144317334213</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005929390845745592</v>
+        <v>0.0004703237279909154</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.405159941180655</v>
+        <v>1.911824389174857</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.000320877361017148</v>
+        <v>0.0002540518768592011</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.405208491925858</v>
+        <v>1.911861972613917</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000152356530210549</v>
+        <v>0.0001197726022376576</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.405191296037819</v>
+        <v>1.911847271824636</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.2411556626069e-05</v>
+        <v>7.273245427736819e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.405223689039313</v>
+        <v>1.911872110684413</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.543908871678713e-05</v>
+        <v>3.514539714193261e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.405223129058629</v>
+        <v>1.911870653856644</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.997732826962944e-05</v>
+        <v>1.498186261570356e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.405216583035514</v>
+        <v>1.911864417038152</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.034975653315254e-05</v>
+        <v>7.791463777627117e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.405218574147311</v>
+        <v>1.911865009306555</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.993667665820105e-06</v>
+        <v>8.280563881834207e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.405212087920634</v>
+        <v>1.911858865510579</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-1.911892527543644e-06</v>
+        <v>-2.941261685029097e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.405206129322495</v>
+        <v>1.911853180976551</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-2.77474353817759e-06</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.405201460053858</v>
+        <v>1.911848429701337</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.405196170906296</v>
+        <v>1.911843140553775</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.405196148171995</v>
+        <v>1.911843117819474</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.405196466452212</v>
+        <v>1.91184343609969</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.405197557698669</v>
+        <v>1.911844527346148</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.405196868091533</v>
+        <v>1.911843837739012</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.405196898403934</v>
+        <v>1.911843868051413</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.405196708951424</v>
+        <v>1.911843678598903</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.405196761998127</v>
+        <v>1.911843731645606</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.40519681504483</v>
+        <v>1.911843784692309</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.405196777154328</v>
+        <v>1.911843746801807</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.405196648326621</v>
+        <v>1.9118436179741</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.405196504342714</v>
+        <v>1.911843473990193</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.405196345202605</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.405196398249308</v>
+        <v>1.911843367896787</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.405196345202605</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.405196345202605</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.405196163328196</v>
+        <v>1.911843132975675</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.405196330046405</v>
+        <v>1.911843299693883</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.405196527077015</v>
+        <v>1.911843496724494</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.405196367936907</v>
+        <v>1.911843337584386</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.405196405827409</v>
+        <v>1.911843375474887</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.405196602858019</v>
+        <v>1.911843572505498</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.405196580123718</v>
+        <v>1.911843549771197</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.40519642856171</v>
+        <v>1.911843398209189</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.405196352780706</v>
+        <v>1.911843322428185</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.405196451296011</v>
+        <v>1.91184342094349</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.405196458874112</v>
+        <v>1.91184342852159</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.405196724107626</v>
+        <v>1.911843693755104</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.40519642856171</v>
+        <v>1.911843398209189</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.405196671060922</v>
+        <v>1.911843640708401</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.405196754420027</v>
+        <v>1.911843724067505</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.405196587701818</v>
+        <v>1.911843557349297</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.405196777154328</v>
+        <v>1.911843746801807</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.40519642856171</v>
+        <v>1.911843398209189</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.405196223952999</v>
+        <v>1.911843193600478</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.405196337624505</v>
+        <v>1.911843307271984</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.405196352780706</v>
+        <v>1.911843322428185</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.405196117859594</v>
+        <v>1.911843087507072</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.405196178484397</v>
+        <v>1.911843148131875</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.40519604965669</v>
+        <v>1.911843019304169</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.405196186062497</v>
+        <v>1.911843155709976</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.405196360358806</v>
+        <v>1.911843330006285</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.405196504342714</v>
+        <v>1.911843473990193</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.405196337624505</v>
+        <v>1.911843307271984</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.405196330046405</v>
+        <v>1.911843299693883</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.40519604207859</v>
+        <v>1.911843011726068</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.405196057234791</v>
+        <v>1.911843026882269</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.405196284577802</v>
+        <v>1.911843254225281</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.405196269421602</v>
+        <v>1.91184323906908</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.405196375515007</v>
+        <v>1.911843345162486</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.405196102703393</v>
+        <v>1.911843072350872</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.405196201218698</v>
+        <v>1.911843170866177</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.405196352780706</v>
+        <v>1.911843322428185</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.405196367936907</v>
+        <v>1.911843337584386</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.405196345202605</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.40519642856171</v>
+        <v>1.911843398209189</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.405196527077015</v>
+        <v>1.911843496724494</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.405196360358806</v>
+        <v>1.911843330006285</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.405196345202605</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.405196314890204</v>
+        <v>1.911843284537683</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.405196299734003</v>
+        <v>1.911843269381482</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.405196337624505</v>
+        <v>1.911843307271984</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.405196352780706</v>
+        <v>1.911843322428185</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.405196345202605</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_2_000007.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7971993478774387</v>
+        <v>0.8337558510012639</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>4.242080543885407</v>
+        <v>1.848448397689915</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>4.242080543885407</v>
+        <v>2.863140944378566</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>4.242080543885407</v>
+        <v>2.863140944378566</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>4.242080543885407</v>
+        <v>2.863140944378566</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>4.242080543885407</v>
+        <v>2.863140944378566</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>4.242080543885407</v>
+        <v>2.863140944378566</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>4.242080543885407</v>
+        <v>2.863140944378566</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>4.242080543885407</v>
+        <v>2.863140944378566</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>4.242080543885407</v>
+        <v>2.863140944378566</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>3.642080543885407</v>
+        <v>2.863140944378566</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>3.642080543885407</v>
+        <v>1.648448397689914</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7971993478774387</v>
+        <v>1.648448397689914</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>3.642080543885407</v>
+        <v>1.648448397689914</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>3.642080543885407</v>
+        <v>1.648448397689914</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7971993478774387</v>
+        <v>0.6337558510012639</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7971993478774387</v>
+        <v>0.6337558510012639</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>4.242080543885407</v>
+        <v>0.6337558510012639</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.1971993478774388</v>
+        <v>0.8337558510012639</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.1971993478774388</v>
+        <v>-0.1809366956873866</v>
       </c>
       <c r="JC39" t="n">
-        <v>-8.49619523214642e-05</v>
+        <v>-8.62021065717563e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.9794857538496202</v>
+        <v>0.9937829007658913</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.960485767463571</v>
+        <v>1.989102162105058</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1468782580559186</v>
+        <v>0.1490221790123778</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.273441819022459</v>
+        <v>1.292029719922858</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1836456704050446</v>
+        <v>0.1863262124467291</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.493878181694815</v>
+        <v>1.515683699768132</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2632551976040997</v>
+        <v>0.2670979045835681</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.836846545878087</v>
+        <v>1.863658335199905</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2816305678435452</v>
+        <v>0.2857418512088893</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC44" t="n">
-        <v>2.136872808447906</v>
+        <v>2.168064047373765</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2984716366441283</v>
+        <v>0.302828768343851</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.452207605419116</v>
+        <v>2.488001354935506</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1346946984107789</v>
+        <v>0.1366603250468715</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.422877192868414</v>
+        <v>2.458242919917558</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.06505202606608947</v>
+        <v>0.06600133388932709</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.418179594771483</v>
+        <v>2.453476769511137</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03099535369839031</v>
+        <v>0.03144767061347004</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.41506661577477</v>
+        <v>2.450318362639324</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.00918151620237293</v>
+        <v>0.009315212238221749</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.402403469464549</v>
+        <v>2.437470495742531</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006071049223727566</v>
+        <v>0.006160445296786681</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.405361177390374</v>
+        <v>2.440471555203413</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003105282126212162</v>
+        <v>0.003150544061614175</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.405496116973147</v>
+        <v>2.440608531236932</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001585526177187189</v>
+        <v>0.001608679406348774</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.405561044259266</v>
+        <v>2.440674476120957</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005929390845745592</v>
+        <v>0.0006020217035807549</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.405159941180655</v>
+        <v>2.440267610162678</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.000320877361017148</v>
+        <v>0.0003258273968806996</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.405208491925858</v>
+        <v>2.440316905098025</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000152356530210549</v>
+        <v>0.0001539459901116657</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.405191296037819</v>
+        <v>2.440299555706796</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.2411556626069e-05</v>
+        <v>9.339551174350403e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.405223689039313</v>
+        <v>2.440332515867885</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.543908871678713e-05</v>
+        <v>4.646845787427258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.405223129058629</v>
+        <v>2.440332045571909</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.405216583035514</v>
+        <v>2.440325469236393</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.034975653315254e-05</v>
+        <v>1.162890291091525e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.405218574147311</v>
+        <v>2.440327739185315</v>
       </c>
     </row>
     <row r="60">
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.405212087920634</v>
+        <v>2.440321252958638</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.405206129322495</v>
+        <v>2.4403152943605</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.405201460053858</v>
+        <v>2.440310625091863</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.405196170906296</v>
+        <v>2.440305335944301</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.405196148171995</v>
+        <v>2.44030531321</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.405196466452212</v>
+        <v>2.440305631490216</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.405197557698669</v>
+        <v>2.440306722736673</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.405196868091533</v>
+        <v>2.440306033129537</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.405196898403934</v>
+        <v>2.440306063441939</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.405196708951424</v>
+        <v>2.440305873989429</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.405196761998127</v>
+        <v>2.440305927036132</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.40519681504483</v>
+        <v>2.440305980082834</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.405196777154328</v>
+        <v>2.440305942192333</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.405196648326621</v>
+        <v>2.440305813364626</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.405196504342714</v>
+        <v>2.440305669380718</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.405196345202605</v>
+        <v>2.44030551024061</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.405196398249308</v>
+        <v>2.440305563287313</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.405196345202605</v>
+        <v>2.44030551024061</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.405196345202605</v>
+        <v>2.44030551024061</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.405196163328196</v>
+        <v>2.4403053283662</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.405196330046405</v>
+        <v>2.440305495084409</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.405196527077015</v>
+        <v>2.440305692115019</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.405196367936907</v>
+        <v>2.440305532974911</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.405196405827409</v>
+        <v>2.440305570865413</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.405196602858019</v>
+        <v>2.440305767896024</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.405196580123718</v>
+        <v>2.440305745161722</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.40519642856171</v>
+        <v>2.440305593599714</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.405196352780706</v>
+        <v>2.44030551781871</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.405196451296011</v>
+        <v>2.440305616334015</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.405196458874112</v>
+        <v>2.440305623912116</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.405196724107626</v>
+        <v>2.44030588914563</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.40519642856171</v>
+        <v>2.440305593599714</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.405196671060922</v>
+        <v>2.440305836098927</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.405196754420027</v>
+        <v>2.440305919458031</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.405196587701818</v>
+        <v>2.440305752739822</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.405196777154328</v>
+        <v>2.440305942192333</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.40519642856171</v>
+        <v>2.440305593599714</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.405196223952999</v>
+        <v>2.440305388991004</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.405196337624505</v>
+        <v>2.44030550266251</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.405196352780706</v>
+        <v>2.44030551781871</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.405196117859594</v>
+        <v>2.440305282897598</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.405196178484397</v>
+        <v>2.440305343522401</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.40519604965669</v>
+        <v>2.440305214694694</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.405196186062497</v>
+        <v>2.440305351100502</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.405196360358806</v>
+        <v>2.440305525396811</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.405196504342714</v>
+        <v>2.440305669380718</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.405196337624505</v>
+        <v>2.44030550266251</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.405196330046405</v>
+        <v>2.440305495084409</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.40519604207859</v>
+        <v>2.440305207116594</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.405196057234791</v>
+        <v>2.440305222272795</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.405196284577802</v>
+        <v>2.440305449615807</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.405196269421602</v>
+        <v>2.440305434459606</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.405196375515007</v>
+        <v>2.440305540553012</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.405196102703393</v>
+        <v>2.440305267741397</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.405196201218698</v>
+        <v>2.440305366256703</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.405196352780706</v>
+        <v>2.44030551781871</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.405196367936907</v>
+        <v>2.440305532974911</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.405196345202605</v>
+        <v>2.44030551024061</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.40519642856171</v>
+        <v>2.440305593599714</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.405196527077015</v>
+        <v>2.440305692115019</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.405196360358806</v>
+        <v>2.440305525396811</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.405196345202605</v>
+        <v>2.44030551024061</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.405196314890204</v>
+        <v>2.440305479928209</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.405196299734003</v>
+        <v>2.440305464772007</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.405196337624505</v>
+        <v>2.44030550266251</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.405196352780706</v>
+        <v>2.44030551781871</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7971993478774387</v>
+        <v>-0.3809366956873866</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.405196345202605</v>
+        <v>2.44030551024061</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_2_000007.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.01068265084177256</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.006198184564709663</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.8599999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.003722447901964188</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.002258118242025375</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.16</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.001473216339945793</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.001064583659172058</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0008403491228818893</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.0006642770022153854</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.0005072299391031265</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.0003865845501422882</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.0002935547381639481</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.0002261027693748474</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.0001250226050615311</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-7.666833698749542e-05</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-1.842156052589417e-05</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.8337558510012639</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>2.591684460639954e-05</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.848448397689915</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.0001031029969453812</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.863140944378566</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.000155031681060791</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.863140944378566</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.0002423115074634552</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.863140944378566</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.0003484152257442474</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.863140944378566</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.0004434902220964432</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.863140944378566</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.0005296338349580765</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.863140944378566</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.000405559316277504</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.863140944378566</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.0002408809959888458</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.863140944378566</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0001100897789001465</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.863140944378566</v>
+        <v>-0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>2.333521842956543e-05</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.648448397689914</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-3.018230199813843e-05</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.648448397689914</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>2.190284430980682e-05</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.648448397689914</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>6.016343832015991e-07</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.648448397689914</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-4.936568439006805e-05</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.6337558510012639</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.0001097824424505234</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.0001643244177103043</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.0001611411571502686</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.00013699010014534</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-3.549829125404358e-05</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.6337558510012639</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.0002184789627790451</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.6337558510012639</v>
+        <v>0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-1.032650470733643e-05</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.8337558510012639</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.0003820080310106277</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.1809366956873866</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-8.62021065717563e-05</v>
+        <v>-5.577029551274609e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.9937829007658913</v>
+        <v>0.6429491398164291</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.0007861331105232239</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.989102162105058</v>
+        <v>1.28689216297079</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1490221790123778</v>
+        <v>0.09641309156731945</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.001106563955545425</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.292029719922858</v>
+        <v>0.8359062801057161</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1863262124467291</v>
+        <v>0.120547678509721</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.001357458531856537</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.515683699768132</v>
+        <v>0.9806039702055612</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2670979045835681</v>
+        <v>0.1728046881330954</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.001403292641043663</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.863658335199905</v>
+        <v>1.205733584935285</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2857418512088893</v>
+        <v>0.1848664391270448</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.001467365771532059</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>2.168064047373765</v>
+        <v>1.402675355715708</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.302828768343851</v>
+        <v>0.1959219016647416</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.001740982756018639</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.488001354935506</v>
+        <v>1.60966601269259</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1366603250468715</v>
+        <v>0.08841591031399536</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.002156196162104607</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.458242919917558</v>
+        <v>1.590413121333953</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.06600133388932709</v>
+        <v>0.04270084349620157</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.003031549975275993</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.453476769511137</v>
+        <v>1.587329567857212</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03144767061347004</v>
+        <v>0.02034568064090336</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.003553804010152817</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.450318362639324</v>
+        <v>1.585286175253105</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.009315212238221749</v>
+        <v>0.006025127182116028</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.003869974985718727</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.437470495742531</v>
+        <v>1.576972233053586</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006160445296786681</v>
+        <v>0.003983218356153405</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.003931797109544277</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.440471555203413</v>
+        <v>1.57891198632568</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003150544061614175</v>
+        <v>0.002036706868677708</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.003965129144489765</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.440608531236932</v>
+        <v>1.578998847962584</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001608679406348774</v>
+        <v>0.001038908636546275</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.003839553333818913</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.440674476120957</v>
+        <v>1.579039751089439</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0006020217035807549</v>
+        <v>0.0003878232720179698</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.003650397062301636</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.440267610162678</v>
+        <v>1.57877469069998</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003258273968806996</v>
+        <v>0.000208676548109978</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.00350493099540472</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.440316905098025</v>
+        <v>1.57880482720277</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001539459901116657</v>
+        <v>9.831489357258269e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.003357233479619026</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.440299555706796</v>
+        <v>1.578791819801533</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.339551174350403e-05</v>
+        <v>5.895708263327761e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.003250795416533947</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.440332515867885</v>
+        <v>1.578811370762109</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.646845787427258e-05</v>
+        <v>2.793981303953445e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.003306160680949688</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.440332045571909</v>
+        <v>1.578809286141381</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.997732826962944e-05</v>
+        <v>1.098549009256284e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.002881014719605446</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.440325469236393</v>
+        <v>1.578803266374186</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.162890291091525e-05</v>
+        <v>5.233171022101693e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.003032345324754715</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.440327739185315</v>
+        <v>1.578803020578622</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.993667665820105e-06</v>
+        <v>-3.375548894532629e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.003500348888337612</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.440321252958638</v>
+        <v>1.578796991870336</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-1.911892527543644e-06</v>
+        <v>-2.941261685029097e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.003773455508053303</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.4403152943605</v>
+        <v>1.578791307336308</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-2.77474353817759e-06</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.003870059736073017</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.440310625091863</v>
+        <v>1.578786556061094</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.003813265822827816</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.440305335944301</v>
+        <v>1.578781266913532</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.003589804284274578</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.44030531321</v>
+        <v>1.578781244179231</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.0032187569886446</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.440305631490216</v>
+        <v>1.578781562459447</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.002934973686933517</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.440306722736673</v>
+        <v>1.578782653705904</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.003513368777930737</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.440306033129537</v>
+        <v>1.578781964098768</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.004418530501425266</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.440306063441939</v>
+        <v>1.57878199441117</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.00505217257887125</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.440305873989429</v>
+        <v>1.57878180495866</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.005343661643564701</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.440305927036132</v>
+        <v>1.578781858005363</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.005466612055897713</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.440305980082834</v>
+        <v>1.578781911052065</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.005399437621235847</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.440305942192333</v>
+        <v>1.578781873161563</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.005175353027880192</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.440305813364626</v>
+        <v>1.578781744333857</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.004882579669356346</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.440305669380718</v>
+        <v>1.578781600349949</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.00456572137773037</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.44030551024061</v>
+        <v>1.578781441209841</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.004294739104807377</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.440305563287313</v>
+        <v>1.578781494256543</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.004111059941351414</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.44030551024061</v>
+        <v>1.578781441209841</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.003931050188839436</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.44030551024061</v>
+        <v>1.578781441209841</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.00366024486720562</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.4403053283662</v>
+        <v>1.578781259335431</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.003480592742562294</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.440305495084409</v>
+        <v>1.57878142605364</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.003539489582180977</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.440305692115019</v>
+        <v>1.57878162308425</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.003626815974712372</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.440305532974911</v>
+        <v>1.578781463944142</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.003569980151951313</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.440305570865413</v>
+        <v>1.578781501834644</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.003524851985275745</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.440305767896024</v>
+        <v>1.578781698865254</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.003664057701826096</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.440305745161722</v>
+        <v>1.578781676130953</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.003803431987762451</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.16</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.440305593599714</v>
+        <v>1.578781524568945</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.00381954200565815</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.44030551781871</v>
+        <v>1.578781448787941</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.003781118430197239</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.440305616334015</v>
+        <v>1.578781547303246</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.003660235553979874</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.16</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.440305623912116</v>
+        <v>1.578781554881347</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.003700947389006615</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.44030588914563</v>
+        <v>1.578781820114861</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.003768983297049999</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.440305593599714</v>
+        <v>1.578781524568945</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.003768804483115673</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.440305836098927</v>
+        <v>1.578781767068158</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.00393994152545929</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.440305919458031</v>
+        <v>1.578781850427262</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.003806371241807938</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.440305752739822</v>
+        <v>1.578781683709053</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.003985481336712837</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.440305942192333</v>
+        <v>1.578781873161563</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.0041656494140625</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.440305593599714</v>
+        <v>1.578781524568945</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.004234523512423038</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.440305388991004</v>
+        <v>1.578781319960235</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.004150218330323696</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.44030550266251</v>
+        <v>1.578781433631741</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.003982767462730408</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.16</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.44030551781871</v>
+        <v>1.578781448787941</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.00375266931951046</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.440305282897598</v>
+        <v>1.578781213866829</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.003605633974075317</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.440305343522401</v>
+        <v>1.578781274491632</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.003432244993746281</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.440305214694694</v>
+        <v>1.578781145663925</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.003136678598821163</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.440305351100502</v>
+        <v>1.578781282069732</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.003148212097585201</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.440305525396811</v>
+        <v>1.578781456366042</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.00330042652785778</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.440305669380718</v>
+        <v>1.578781600349949</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.003375311382114887</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.44030550266251</v>
+        <v>1.578781433631741</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.003446932882070541</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.440305495084409</v>
+        <v>1.57878142605364</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.003429791890084743</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.440305207116594</v>
+        <v>1.578781138085825</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.003300217911601067</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.440305222272795</v>
+        <v>1.578781153242026</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.003219936974346638</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.440305449615807</v>
+        <v>1.578781380585038</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.003119707107543945</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.440305434459606</v>
+        <v>1.578781365428837</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.00320099201053381</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.440305540553012</v>
+        <v>1.578781471522242</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.003203220665454865</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.440305267741397</v>
+        <v>1.578781198710628</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.003137806430459023</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.440305366256703</v>
+        <v>1.578781297225933</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.003128344193100929</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.44030551781871</v>
+        <v>1.578781448787941</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.003160840831696987</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.440305532974911</v>
+        <v>1.578781463944142</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.003192116506397724</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.44030551024061</v>
+        <v>1.578781441209841</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.003217079676687717</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.16</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.440305593599714</v>
+        <v>1.578781524568945</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.003340310417115688</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.440305692115019</v>
+        <v>1.57878162308425</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.003435377031564713</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.440305525396811</v>
+        <v>1.578781456366042</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.00344450119882822</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.44030551024061</v>
+        <v>1.578781441209841</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.003407564014196396</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.16</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.440305479928209</v>
+        <v>1.578781410897439</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.003353381529450417</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3809366956873866</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.440305464772007</v>
+        <v>1.578781395741238</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.003327852115035057</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.44030550266251</v>
+        <v>1.578781433631741</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.003295295871794224</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3809366956873866</v>
+        <v>0.9299999999999999</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.44030551781871</v>
+        <v>1.578781448787941</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.003255045041441917</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3809366956873866</v>
+        <v>1.14</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.44030551024061</v>
+        <v>1.578781441209841</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_2_000007.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000007.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.01068265084177256</v>
+        <v>-0.01068264525383711</v>
       </c>
       <c r="JB2" t="n">
         <v>-1.28</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.006198184564709663</v>
+        <v>-0.006198177114129066</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.8599999999999997</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.003722447901964188</v>
+        <v>-0.003722445107996464</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.4399999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.002258118242025375</v>
+        <v>-0.002258112654089928</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.16</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.001473216339945793</v>
+        <v>-0.001473207026720047</v>
       </c>
       <c r="JB6" t="n">
         <v>0.7199999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.001064583659172058</v>
+        <v>-0.00106457993388176</v>
       </c>
       <c r="JB7" t="n">
         <v>0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.0008403491228818893</v>
+        <v>-0.0008403416723012924</v>
       </c>
       <c r="JB8" t="n">
         <v>0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.0006642770022153854</v>
+        <v>-0.0006642621010541916</v>
       </c>
       <c r="JB9" t="n">
         <v>0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.0005072299391031265</v>
+        <v>-0.0005072131752967834</v>
       </c>
       <c r="JB10" t="n">
         <v>0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.0002935547381639481</v>
+        <v>-0.0002935603260993958</v>
       </c>
       <c r="JB12" t="n">
         <v>0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.0002261027693748474</v>
+        <v>-0.0002261046320199966</v>
       </c>
       <c r="JB13" t="n">
         <v>0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.0001250226050615311</v>
+        <v>-0.0001250132918357849</v>
       </c>
       <c r="JB14" t="n">
         <v>0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-7.666833698749542e-05</v>
+        <v>-7.665902376174927e-05</v>
       </c>
       <c r="JB15" t="n">
         <v>0.9999999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-1.842156052589417e-05</v>
+        <v>-1.840479671955109e-05</v>
       </c>
       <c r="JB16" t="n">
         <v>0.3999999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>2.591684460639954e-05</v>
+        <v>2.593174576759338e-05</v>
       </c>
       <c r="JB17" t="n">
         <v>0.3999999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.0001031029969453812</v>
+        <v>0.0001031253486871719</v>
       </c>
       <c r="JB18" t="n">
         <v>0.3999999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.000155031681060791</v>
+        <v>0.0001550409942865372</v>
       </c>
       <c r="JB19" t="n">
         <v>0.3999999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.0002423115074634552</v>
+        <v>0.0002423357218503952</v>
       </c>
       <c r="JB20" t="n">
         <v>0.3999999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.0003484152257442474</v>
+        <v>0.0003484487533569336</v>
       </c>
       <c r="JB21" t="n">
         <v>0.3999999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.0004434902220964432</v>
+        <v>0.0004435125738382339</v>
       </c>
       <c r="JB22" t="n">
         <v>0.3999999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.0005296338349580765</v>
+        <v>0.0005296450108289719</v>
       </c>
       <c r="JB23" t="n">
         <v>0.2599999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.000405559316277504</v>
+        <v>0.0004055686295032501</v>
       </c>
       <c r="JB24" t="n">
         <v>0.1199999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.0002408809959888458</v>
+        <v>0.0002408977597951889</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.02000000000000007</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.0001100897789001465</v>
+        <v>0.0001101084053516388</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.16</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>2.333521842956543e-05</v>
+        <v>2.335011959075928e-05</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.3</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-3.018230199813843e-05</v>
+        <v>-3.016926348209381e-05</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.3</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>2.190284430980682e-05</v>
+        <v>2.192333340644836e-05</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.3</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>6.016343832015991e-07</v>
+        <v>6.146728992462158e-07</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.3</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-4.936568439006805e-05</v>
+        <v>-4.935078322887421e-05</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.3</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.0001097824424505234</v>
+        <v>-0.0001097675412893295</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.3</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.0001643244177103043</v>
+        <v>-0.0001643151044845581</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.3</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.0001611411571502686</v>
+        <v>-0.0001611318439245224</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.3</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-3.549829125404358e-05</v>
+        <v>-3.548339009284973e-05</v>
       </c>
       <c r="JB36" t="n">
         <v>0.4399999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.0002184789627790451</v>
+        <v>0.0002184882760047913</v>
       </c>
       <c r="JB37" t="n">
         <v>0.3</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-1.032650470733643e-05</v>
+        <v>-1.03190541267395e-05</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.4399999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.0003820080310106277</v>
+        <v>-0.0003820005804300308</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.5799999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.0007861331105232239</v>
+        <v>-0.0007861107587814331</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.8599999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.001106563955545425</v>
+        <v>-0.001106550917029381</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.001357458531856537</v>
+        <v>-0.001357449218630791</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.001403292641043663</v>
+        <v>-0.001403285190463066</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.001467365771532059</v>
+        <v>-0.001467358320951462</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.001740982756018639</v>
+        <v>-0.001740990206599236</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.002156196162104607</v>
+        <v>-0.00215616449713707</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.003031549975275993</v>
+        <v>-0.00303153321146965</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.003553804010152817</v>
+        <v>-0.003553805872797966</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.003869974985718727</v>
+        <v>-0.003870011307299137</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.003931797109544277</v>
+        <v>-0.003931804560124874</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.003965129144489765</v>
+        <v>-0.003965145908296108</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.003839553333818913</v>
+        <v>-0.003839566372334957</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.003650397062301636</v>
+        <v>-0.003650405444204807</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.00350493099540472</v>
+        <v>-0.003504931926727295</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.003357233479619026</v>
+        <v>-0.003357253037393093</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.003250795416533947</v>
+        <v>-0.003250786103308201</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.003306160680949688</v>
+        <v>-0.003306156024336815</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.002881014719605446</v>
+        <v>-0.002881016582250595</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.003032345324754715</v>
+        <v>-0.003032337874174118</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.003500348888337612</v>
+        <v>-0.00350034236907959</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.003773455508053303</v>
+        <v>-0.003773465752601624</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.003870059736073017</v>
+        <v>-0.003870075568556786</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.003813265822827816</v>
+        <v>-0.003813270479440689</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.003589804284274578</v>
+        <v>-0.003589834086596966</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.0032187569886446</v>
+        <v>-0.003218785859644413</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.002934973686933517</v>
+        <v>-0.002934953197836876</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.003513368777930737</v>
+        <v>-0.003513307310640812</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.004418530501425266</v>
+        <v>-0.004418479278683662</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.00505217257887125</v>
+        <v>-0.005052185617387295</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.005343661643564701</v>
+        <v>-0.005343726836144924</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.005466612055897713</v>
+        <v>-0.005466657690703869</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.005399437621235847</v>
+        <v>-0.005399483256042004</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.005175353027880192</v>
+        <v>-0.005175379104912281</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.004882579669356346</v>
+        <v>-0.00488259457051754</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.00456572137773037</v>
+        <v>-0.004565732553601265</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.004294739104807377</v>
+        <v>-0.004294737242162228</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.2599999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.004111059941351414</v>
+        <v>-0.004111047834157944</v>
       </c>
       <c r="JB77" t="n">
         <v>0.02000000000000007</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.003931050188839436</v>
+        <v>-0.003931064158678055</v>
       </c>
       <c r="JB78" t="n">
         <v>0.3</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.00366024486720562</v>
+        <v>-0.003660253249108791</v>
       </c>
       <c r="JB79" t="n">
         <v>0.5799999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.003480592742562294</v>
+        <v>-0.003480608575046062</v>
       </c>
       <c r="JB80" t="n">
         <v>0.8599999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.003539489582180977</v>
+        <v>-0.003539497964084148</v>
       </c>
       <c r="JB81" t="n">
         <v>0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.003626815974712372</v>
+        <v>-0.003626829013228416</v>
       </c>
       <c r="JB82" t="n">
         <v>0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.003569980151951313</v>
+        <v>-0.003569998778402805</v>
       </c>
       <c r="JB83" t="n">
         <v>0.8599999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.003524851985275745</v>
+        <v>-0.003524882718920708</v>
       </c>
       <c r="JB84" t="n">
         <v>0.7199999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.003664057701826096</v>
+        <v>-0.003664080984890461</v>
       </c>
       <c r="JB85" t="n">
         <v>0.5799999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.003803431987762451</v>
+        <v>-0.003803453408181667</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.16</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.00381954200565815</v>
+        <v>-0.003819573670625687</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.3</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.003781118430197239</v>
+        <v>-0.003781129606068134</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.3</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.003660235553979874</v>
+        <v>-0.003660248592495918</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.16</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.003700947389006615</v>
+        <v>-0.003700966946780682</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.02000000000000007</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.003768983297049999</v>
+        <v>-0.003769028000533581</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.02000000000000007</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.003768804483115673</v>
+        <v>-0.003768831491470337</v>
       </c>
       <c r="JB92" t="n">
         <v>0.5799999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.00393994152545929</v>
+        <v>-0.003939944319427013</v>
       </c>
       <c r="JB93" t="n">
         <v>0.5799999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.003806371241807938</v>
+        <v>-0.003806373104453087</v>
       </c>
       <c r="JB94" t="n">
         <v>0.4399999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.003985481336712837</v>
+        <v>-0.003985472023487091</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.4399999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.0041656494140625</v>
+        <v>-0.004165643826127052</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.4399999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.004234523512423038</v>
+        <v>-0.004234550520777702</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.4399999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.004150218330323696</v>
+        <v>-0.004150215536355972</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.3</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.003982767462730408</v>
+        <v>-0.003982769325375557</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.16</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.00375266931951046</v>
+        <v>-0.003752671182155609</v>
       </c>
       <c r="JB100" t="n">
         <v>0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.003605633974075317</v>
+        <v>-0.003605627454817295</v>
       </c>
       <c r="JB101" t="n">
         <v>0.8599999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.003432244993746281</v>
+        <v>-0.003432241268455982</v>
       </c>
       <c r="JB102" t="n">
         <v>0.9999999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.003136678598821163</v>
+        <v>-0.003136690706014633</v>
       </c>
       <c r="JB103" t="n">
         <v>0.9999999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.003148212097585201</v>
+        <v>-0.003148198127746582</v>
       </c>
       <c r="JB104" t="n">
         <v>0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.003375311382114887</v>
+        <v>-0.003375312313437462</v>
       </c>
       <c r="JB106" t="n">
         <v>0.7199999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.003446932882070541</v>
+        <v>-0.003446946851909161</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.02000000000000007</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.003429791890084743</v>
+        <v>-0.003429792821407318</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.02000000000000007</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.003300217911601067</v>
+        <v>-0.003300216980278492</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.02000000000000007</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.003219936974346638</v>
+        <v>-0.003219958394765854</v>
       </c>
       <c r="JB110" t="n">
         <v>0.1199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.003119707107543945</v>
+        <v>-0.003119711764156818</v>
       </c>
       <c r="JB111" t="n">
         <v>0.2599999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.00320099201053381</v>
+        <v>-0.003200987353920937</v>
       </c>
       <c r="JB112" t="n">
         <v>0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.003203220665454865</v>
+        <v>-0.00320321973413229</v>
       </c>
       <c r="JB113" t="n">
         <v>0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.003137806430459023</v>
+        <v>-0.003137815743684769</v>
       </c>
       <c r="JB114" t="n">
         <v>0.8599999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.003128344193100929</v>
+        <v>-0.003128347918391228</v>
       </c>
       <c r="JB115" t="n">
         <v>0.8599999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.003160840831696987</v>
+        <v>-0.003160855732858181</v>
       </c>
       <c r="JB116" t="n">
         <v>0.7199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.003192116506397724</v>
+        <v>-0.003192123956978321</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.02000000000000007</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.003217079676687717</v>
+        <v>-0.003217091783881187</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.16</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.003435377031564713</v>
+        <v>-0.003435391001403332</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.3</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.00344450119882822</v>
+        <v>-0.003444497473537922</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.3</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.003407564014196396</v>
+        <v>-0.0034075528383255</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.16</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.003353381529450417</v>
+        <v>-0.003353375941514969</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.02000000000000007</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.003327852115035057</v>
+        <v>-0.003327867947518826</v>
       </c>
       <c r="JB124" t="n">
         <v>0.7199999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.003295295871794224</v>
+        <v>-0.003295299597084522</v>
       </c>
       <c r="JB125" t="n">
         <v>0.9299999999999999</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.003255045041441917</v>
+        <v>-0.003255044110119343</v>
       </c>
       <c r="JB126" t="n">
         <v>1.14</v>
